--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48790022-E193-4BD7-85E4-76FFADD068DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49703D1D-97E3-4EF5-9625-51C9D1F0A094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
   <sheets>
     <sheet name="ETF" sheetId="1" r:id="rId1"/>
@@ -89,12 +89,6 @@
     <t>VanEck Quantum Computing UCITS ETF</t>
   </si>
   <si>
-    <t>iShares Global Clean Energy ETF</t>
-  </si>
-  <si>
-    <t>iShares MSCI Global Semiconductors UCITS ETF</t>
-  </si>
-  <si>
     <t>ISIN</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>DFEN.DE</t>
   </si>
   <si>
-    <t>Global X U.S Infrastructure development UCITS ETF</t>
-  </si>
-  <si>
     <t>94VE.DE</t>
   </si>
   <si>
@@ -191,9 +182,6 @@
     <t>Bioteknologi</t>
   </si>
   <si>
-    <t>Xtrackers MSCI World Industrials</t>
-  </si>
-  <si>
     <t>Industri</t>
   </si>
   <si>
@@ -201,6 +189,18 @@
   </si>
   <si>
     <t>Kontant</t>
+  </si>
+  <si>
+    <t>Global X U.S Infrastructure Development UCITS ETF</t>
+  </si>
+  <si>
+    <t>iShs Global Clean Energy ETF</t>
+  </si>
+  <si>
+    <t>iShs MSCI Global Semiconductors UCITS ETF</t>
+  </si>
+  <si>
+    <t>Xtrackers MSCI World Industrials UCITS ETF 1C</t>
   </si>
 </sst>
 </file>
@@ -242,14 +242,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,13 +595,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
@@ -627,13 +624,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -656,13 +653,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>59</v>
@@ -670,7 +667,7 @@
       <c r="E3" s="3">
         <v>43.5</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3">
         <v>46</v>
       </c>
       <c r="G3" s="1">
@@ -688,10 +685,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>52</v>
@@ -699,7 +696,7 @@
       <c r="E4" s="3">
         <v>29</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4">
         <v>23</v>
       </c>
       <c r="G4" s="1">
@@ -709,18 +706,18 @@
         <v>-2318.16</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>185</v>
@@ -728,7 +725,7 @@
       <c r="E5" s="3">
         <v>10.6</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>10</v>
       </c>
       <c r="G5" s="1">
@@ -738,18 +735,18 @@
         <v>-824.72999999999945</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>468</v>
@@ -757,7 +754,7 @@
       <c r="E6" s="3">
         <v>10.6</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6">
         <v>19</v>
       </c>
       <c r="G6" s="1">
@@ -775,25 +772,25 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>118.4</v>
-      </c>
-      <c r="F7" s="3">
+        <v>115.37</v>
+      </c>
+      <c r="F7">
         <v>114</v>
       </c>
       <c r="G7" s="1">
         <v>16940.399999999998</v>
       </c>
       <c r="H7" s="1">
-        <v>-653.84000000000083</v>
+        <v>-274.83570000000088</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -801,13 +798,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D8">
         <v>154</v>
@@ -830,13 +827,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>44</v>
@@ -844,7 +841,7 @@
       <c r="E9" s="3">
         <v>57.12</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9">
         <v>51</v>
       </c>
       <c r="G9" s="1">
@@ -859,13 +856,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>47</v>
@@ -873,7 +870,7 @@
       <c r="E10" s="3">
         <v>27.972000000000001</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10">
         <v>26</v>
       </c>
       <c r="G10" s="1">
@@ -888,13 +885,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11">
         <v>161</v>
@@ -902,7 +899,7 @@
       <c r="E11" s="3">
         <v>16.5</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11">
         <v>14</v>
       </c>
       <c r="G11" s="1">
@@ -917,13 +914,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12">
         <v>46</v>
@@ -946,10 +943,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D13">
         <v>15</v>
@@ -957,7 +954,7 @@
       <c r="E13" s="3">
         <v>95</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13">
         <v>79</v>
       </c>
       <c r="G13" s="1">
@@ -967,15 +964,15 @@
         <v>-1783.1999999999998</v>
       </c>
       <c r="I13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>51</v>
+      <c r="A14" t="s">
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D14">
         <v>17</v>
@@ -983,7 +980,7 @@
       <c r="E14" s="3">
         <v>77.56</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14">
         <v>76</v>
       </c>
       <c r="G14" s="1">
@@ -993,18 +990,18 @@
         <v>-197.04360000000028</v>
       </c>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G16" s="1">
-        <v>29170</v>
+        <v>28372</v>
       </c>
       <c r="I16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49703D1D-97E3-4EF5-9625-51C9D1F0A094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E3EE1E-9E95-434A-85B9-C3F28496B9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
+    <workbookView xWindow="-57705" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
   <sheets>
     <sheet name="ETF" sheetId="1" r:id="rId1"/>
@@ -697,7 +697,7 @@
         <v>29</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
         <v>8886.2799999999988</v>
@@ -755,7 +755,7 @@
         <v>10.6</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1">
         <v>66067.56</v>
@@ -784,7 +784,7 @@
         <v>115.37</v>
       </c>
       <c r="F7">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G7" s="1">
         <v>16940.399999999998</v>
@@ -842,7 +842,7 @@
         <v>57.12</v>
       </c>
       <c r="F9">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1">
         <v>16672.919999999998</v>
@@ -871,7 +871,7 @@
         <v>27.972000000000001</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1">
         <v>9079.4599999999991</v>
@@ -900,7 +900,7 @@
         <v>16.5</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1">
         <v>16747.22</v>
@@ -955,7 +955,7 @@
         <v>95</v>
       </c>
       <c r="F13">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G13" s="1">
         <v>8804.5499999999993</v>
@@ -981,7 +981,7 @@
         <v>77.56</v>
       </c>
       <c r="F14">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" s="1">
         <v>9599.56</v>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E3EE1E-9E95-434A-85B9-C3F28496B9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C6AB4B-7952-4ED7-9AD5-D07C5006000C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57705" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
   <sheets>
     <sheet name="ETF" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t>VanEck S&amp;P Global Mining UCITS ETF</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>Xtrackers MSCI World Industrials UCITS ETF 1C</t>
+  </si>
+  <si>
+    <t>IE00BYXG2H39</t>
+  </si>
+  <si>
+    <t>IE00BM67HV82</t>
   </si>
 </sst>
 </file>
@@ -801,7 +807,7 @@
         <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
@@ -830,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
@@ -859,7 +865,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
@@ -888,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
@@ -917,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
         <v>40</v>
@@ -945,6 +951,9 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
       <c r="C13" t="s">
         <v>46</v>
       </c>
@@ -970,6 +979,9 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
       </c>
       <c r="C14" t="s">
         <v>49</v>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C6AB4B-7952-4ED7-9AD5-D07C5006000C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A12765-0B0D-4411-B181-15775A116F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
@@ -810,7 +810,7 @@
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D8">
         <v>154</v>
@@ -839,7 +839,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D9">
         <v>44</v>
@@ -868,7 +868,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D10">
         <v>47</v>
@@ -897,7 +897,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D11">
         <v>161</v>
@@ -926,7 +926,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12">
         <v>46</v>
@@ -955,7 +955,7 @@
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D13">
         <v>15</v>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A12765-0B0D-4411-B181-15775A116F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCCF24-CC5E-4096-B0DE-619FF1BD6915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
   <sheets>
     <sheet name="ETF" sheetId="1" r:id="rId1"/>
@@ -645,13 +645,13 @@
         <v>60.82</v>
       </c>
       <c r="F2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1">
-        <v>9659</v>
+        <v>9844.75</v>
       </c>
       <c r="H2" s="3">
-        <v>-1638.3149999999998</v>
+        <v>-1452.5650000000001</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -706,10 +706,10 @@
         <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>8886.2799999999988</v>
+        <v>8499.92</v>
       </c>
       <c r="H4" s="1">
-        <v>-2318.16</v>
+        <v>-2704.52</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>29</v>
@@ -764,10 +764,10 @@
         <v>18</v>
       </c>
       <c r="G6" s="1">
-        <v>66067.56</v>
+        <v>62590.32</v>
       </c>
       <c r="H6" s="1">
-        <v>29208.816000000003</v>
+        <v>25731.576000000001</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -790,13 +790,13 @@
         <v>115.37</v>
       </c>
       <c r="F7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G7" s="1">
-        <v>16940.399999999998</v>
+        <v>21064.05</v>
       </c>
       <c r="H7" s="1">
-        <v>-274.83570000000088</v>
+        <v>-2080.3257000000008</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -819,16 +819,16 @@
         <v>8.6419999999999995</v>
       </c>
       <c r="F8" s="3">
-        <v>8.6210000000000004</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>9864.3206200000004</v>
+        <v>9153.76</v>
       </c>
       <c r="H8" s="1">
-        <v>-24.028619999998877</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>11</v>
+        <v>-734.58923999999934</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -851,13 +851,13 @@
         <v>50</v>
       </c>
       <c r="G9" s="1">
-        <v>16672.919999999998</v>
+        <v>16346</v>
       </c>
       <c r="H9" s="1">
-        <v>-2000.7503999999988</v>
+        <v>-2327.6703999999991</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -877,16 +877,16 @@
         <v>27.972000000000001</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1">
-        <v>9079.4599999999991</v>
+        <v>8381.0399999999991</v>
       </c>
       <c r="H10" s="1">
-        <v>-688.64212000000043</v>
+        <v>-1387.0621200000003</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -909,12 +909,12 @@
         <v>13</v>
       </c>
       <c r="G11" s="1">
-        <v>16747.22</v>
+        <v>15550.99</v>
       </c>
       <c r="H11" s="1">
-        <v>-2990.5749999999998</v>
-      </c>
-      <c r="I11" t="s">
+        <v>-4186.8050000000003</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -935,16 +935,16 @@
         <v>55.45</v>
       </c>
       <c r="F12">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" s="1">
-        <v>17089</v>
+        <v>16747.22</v>
       </c>
       <c r="H12" s="1">
-        <v>-1862.7010000000009</v>
+        <v>-2204.4810000000011</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -964,16 +964,16 @@
         <v>95</v>
       </c>
       <c r="F13">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G13" s="1">
-        <v>8804.5499999999993</v>
+        <v>8135.8499999999995</v>
       </c>
       <c r="H13" s="1">
-        <v>-1783.1999999999998</v>
+        <v>-2451.9</v>
       </c>
       <c r="I13" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -993,7 +993,7 @@
         <v>77.56</v>
       </c>
       <c r="F14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="1">
         <v>9599.56</v>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCCF24-CC5E-4096-B0DE-619FF1BD6915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C97420-74C1-43B7-859F-A36F7421DF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
@@ -645,13 +645,13 @@
         <v>60.82</v>
       </c>
       <c r="F2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G2" s="1">
-        <v>9844.75</v>
+        <v>9287.5</v>
       </c>
       <c r="H2" s="3">
-        <v>-1452.5650000000001</v>
+        <v>-2009.8149999999998</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -703,13 +703,13 @@
         <v>29</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1">
-        <v>8499.92</v>
+        <v>7727.2</v>
       </c>
       <c r="H4" s="1">
-        <v>-2704.52</v>
+        <v>-3477.24</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>29</v>
@@ -732,13 +732,13 @@
         <v>10.6</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>13745.5</v>
+        <v>12370.949999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>-824.72999999999945</v>
+        <v>-2199.2799999999993</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>29</v>
@@ -761,13 +761,13 @@
         <v>10.6</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1">
-        <v>62590.32</v>
+        <v>52166.03</v>
       </c>
       <c r="H6" s="1">
-        <v>25731.576000000001</v>
+        <v>22646.194200000002</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -790,13 +790,13 @@
         <v>115.37</v>
       </c>
       <c r="F7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G7" s="1">
-        <v>21064.05</v>
+        <v>14399.34</v>
       </c>
       <c r="H7" s="1">
-        <v>-2080.3257000000008</v>
+        <v>-1716.4860300000009</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -906,13 +906,13 @@
         <v>16.5</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>15550.99</v>
+        <v>14354.76</v>
       </c>
       <c r="H11" s="1">
-        <v>-4186.8050000000003</v>
+        <v>-5383.0349999999999</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>12</v>
@@ -935,13 +935,13 @@
         <v>55.45</v>
       </c>
       <c r="F12">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G12" s="1">
-        <v>16747.22</v>
+        <v>16405.439999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>-2204.4810000000011</v>
+        <v>-2546.2610000000009</v>
       </c>
       <c r="I12" t="s">
         <v>12</v>
@@ -964,13 +964,13 @@
         <v>95</v>
       </c>
       <c r="F13">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G13" s="1">
-        <v>8135.8499999999995</v>
+        <v>7801.5</v>
       </c>
       <c r="H13" s="1">
-        <v>-2451.9</v>
+        <v>-2786.25</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
@@ -993,13 +993,13 @@
         <v>77.56</v>
       </c>
       <c r="F14">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" s="1">
-        <v>9599.56</v>
+        <v>9473.25</v>
       </c>
       <c r="H14" s="1">
-        <v>-197.04360000000028</v>
+        <v>-323.35360000000026</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C97420-74C1-43B7-859F-A36F7421DF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6955AC-B4AF-4BD6-9CF5-0AFA44DF533B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
   <sheets>
     <sheet name="ETF" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>468</v>
+        <v>413</v>
       </c>
       <c r="E6" s="3">
         <v>10.6</v>
@@ -784,7 +784,7 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3">
         <v>115.37</v>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6955AC-B4AF-4BD6-9CF5-0AFA44DF533B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8277842B-0BCF-4442-8131-86554FFD8826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
   <sheets>
     <sheet name="ETF" sheetId="1" r:id="rId1"/>
@@ -645,13 +645,13 @@
         <v>60.82</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1">
-        <v>9287.5</v>
+        <v>10030.5</v>
       </c>
       <c r="H2" s="3">
-        <v>-2009.8149999999998</v>
+        <v>-1266.8150000000001</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -703,13 +703,13 @@
         <v>29</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>7727.2</v>
+        <v>8499.92</v>
       </c>
       <c r="H4" s="1">
-        <v>-3477.24</v>
+        <v>-2704.52</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>29</v>
@@ -758,16 +758,16 @@
         <v>413</v>
       </c>
       <c r="E6" s="3">
-        <v>10.6</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1">
-        <v>52166.03</v>
+        <v>55234.619999999995</v>
       </c>
       <c r="H6" s="1">
-        <v>22646.194200000002</v>
+        <v>25714.784200000002</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -787,16 +787,16 @@
         <v>19</v>
       </c>
       <c r="E7" s="3">
-        <v>115.37</v>
+        <v>114.15900000000001</v>
       </c>
       <c r="F7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G7" s="1">
-        <v>14399.34</v>
+        <v>14964.019999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>-1716.4860300000009</v>
+        <v>-1151.8060300000009</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -848,13 +848,13 @@
         <v>57.12</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1">
-        <v>16346</v>
+        <v>16672.919999999998</v>
       </c>
       <c r="H9" s="1">
-        <v>-2327.6703999999991</v>
+        <v>-2000.7503999999988</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>11</v>
@@ -935,13 +935,13 @@
         <v>55.45</v>
       </c>
       <c r="F12">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G12" s="1">
-        <v>16405.439999999999</v>
+        <v>17089</v>
       </c>
       <c r="H12" s="1">
-        <v>-2546.2610000000009</v>
+        <v>-1862.7010000000009</v>
       </c>
       <c r="I12" t="s">
         <v>12</v>
@@ -964,13 +964,13 @@
         <v>95</v>
       </c>
       <c r="F13">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G13" s="1">
-        <v>7801.5</v>
+        <v>8135.8499999999995</v>
       </c>
       <c r="H13" s="1">
-        <v>-2786.25</v>
+        <v>-2451.9</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
@@ -1010,7 +1010,7 @@
         <v>50</v>
       </c>
       <c r="G16" s="1">
-        <v>28372</v>
+        <v>40976</v>
       </c>
       <c r="I16" t="s">
         <v>50</v>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8277842B-0BCF-4442-8131-86554FFD8826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D34AC9E-C053-4616-A335-D347AA5B7094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
@@ -167,9 +167,6 @@
     <t>94VE.DE</t>
   </si>
   <si>
-    <t>COPX.L</t>
-  </si>
-  <si>
     <t>VVMX.DE</t>
   </si>
   <si>
@@ -207,6 +204,9 @@
   </si>
   <si>
     <t>IE00BM67HV82</t>
+  </si>
+  <si>
+    <t>4COP.DE</t>
   </si>
 </sst>
 </file>
@@ -636,22 +636,22 @@
         <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3">
-        <v>60.82</v>
+        <v>58.79</v>
       </c>
       <c r="F2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1">
-        <v>10030.5</v>
+        <v>14659.651599999999</v>
       </c>
       <c r="H2" s="3">
-        <v>-1266.8150000000001</v>
+        <v>-1601.4977879999997</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -668,19 +668,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E3" s="3">
-        <v>43.5</v>
+        <v>44.308</v>
       </c>
       <c r="F3">
-        <v>46</v>
+        <v>47.48</v>
       </c>
       <c r="G3" s="1">
-        <v>20165.02</v>
+        <v>26265.670112</v>
       </c>
       <c r="H3" s="1">
-        <v>1095.925</v>
+        <v>1754.7326367999983</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>9</v>
@@ -700,16 +700,16 @@
         <v>52</v>
       </c>
       <c r="E4" s="3">
-        <v>29</v>
+        <v>28.96</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1">
-        <v>8499.92</v>
+        <v>8163.3552</v>
       </c>
       <c r="H4" s="1">
-        <v>-2704.52</v>
+        <v>-3094.3003520000007</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>29</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -729,16 +729,16 @@
         <v>185</v>
       </c>
       <c r="E5" s="3">
-        <v>10.6</v>
+        <v>10.622</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="G5" s="1">
-        <v>12370.949999999999</v>
+        <v>12861.769800000002</v>
       </c>
       <c r="H5" s="1">
-        <v>-2199.2799999999993</v>
+        <v>-1828.307491999999</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>29</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -761,13 +761,13 @@
         <v>9.6199999999999992</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1">
-        <v>55234.619999999995</v>
+        <v>49398.764799999997</v>
       </c>
       <c r="H6" s="1">
-        <v>25714.784200000002</v>
+        <v>19697.757464000002</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -790,13 +790,13 @@
         <v>114.15900000000001</v>
       </c>
       <c r="F7">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G7" s="1">
-        <v>14964.019999999999</v>
+        <v>14203.64</v>
       </c>
       <c r="H7" s="1">
-        <v>-1151.8060300000009</v>
+        <v>-2011.0933876000011</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -804,13 +804,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
         <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
       </c>
       <c r="D8">
         <v>154</v>
@@ -822,13 +822,13 @@
         <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>9153.76</v>
+        <v>9209.9392000000007</v>
       </c>
       <c r="H8" s="1">
-        <v>-734.58923999999934</v>
+        <v>-739.09762079999928</v>
       </c>
       <c r="I8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -845,16 +845,16 @@
         <v>44</v>
       </c>
       <c r="E9" s="3">
-        <v>57.12</v>
+        <v>56.9</v>
       </c>
       <c r="F9">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G9" s="1">
-        <v>16672.919999999998</v>
+        <v>17433.099200000001</v>
       </c>
       <c r="H9" s="1">
-        <v>-2000.7503999999988</v>
+        <v>-1282.8129599999995</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>11</v>
@@ -880,10 +880,10 @@
         <v>24</v>
       </c>
       <c r="G10" s="1">
-        <v>8381.0399999999991</v>
+        <v>8432.4768000000004</v>
       </c>
       <c r="H10" s="1">
-        <v>-1387.0621200000003</v>
+        <v>-1395.5749104000004</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -897,22 +897,22 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11">
         <v>161</v>
       </c>
       <c r="E11" s="3">
-        <v>16.5</v>
+        <v>16.594000000000001</v>
       </c>
       <c r="F11">
         <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>14354.76</v>
+        <v>14442.859200000001</v>
       </c>
       <c r="H11" s="1">
-        <v>-5383.0349999999999</v>
+        <v>-5529.2079304000017</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>12</v>
@@ -938,10 +938,10 @@
         <v>50</v>
       </c>
       <c r="G12" s="1">
-        <v>17089</v>
+        <v>17193.88</v>
       </c>
       <c r="H12" s="1">
-        <v>-1862.7010000000009</v>
+        <v>-1874.1329200000009</v>
       </c>
       <c r="I12" t="s">
         <v>12</v>
@@ -961,16 +961,16 @@
         <v>15</v>
       </c>
       <c r="E13" s="3">
-        <v>95</v>
+        <v>95.08</v>
       </c>
       <c r="F13">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G13" s="1">
-        <v>8135.8499999999995</v>
+        <v>7737.2460000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>-2451.9</v>
+        <v>-2924.4547199999997</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
@@ -978,13 +978,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14">
         <v>17</v>
@@ -993,27 +993,27 @@
         <v>77.56</v>
       </c>
       <c r="F14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="1">
-        <v>9473.25</v>
+        <v>9658.4752000000008</v>
       </c>
       <c r="H14" s="1">
-        <v>-323.35360000000026</v>
+        <v>-198.25291200000029</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G16" s="1">
         <v>40976</v>
       </c>
       <c r="I16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/AI_ETF.xlsx
+++ b/AI_ETF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D34AC9E-C053-4616-A335-D347AA5B7094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A000D22-2C2A-4D20-936A-F72A7D5E47E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A961EB-8210-4A19-AADA-AC5A6F1AA134}"/>
   </bookViews>
@@ -674,10 +674,10 @@
         <v>44.308</v>
       </c>
       <c r="F3">
-        <v>47.48</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1">
-        <v>26265.670112</v>
+        <v>24893.748</v>
       </c>
       <c r="H3" s="1">
         <v>1754.7326367999983</v>
@@ -755,16 +755,16 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>413</v>
+        <v>363</v>
       </c>
       <c r="E6" s="3">
-        <v>9.6199999999999992</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1">
-        <v>49398.764799999997</v>
+        <v>46131.927600000003</v>
       </c>
       <c r="H6" s="1">
         <v>19697.757464000002</v>
@@ -790,10 +790,10 @@
         <v>114.15900000000001</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G7" s="1">
-        <v>14203.64</v>
+        <v>13777.5308</v>
       </c>
       <c r="H7" s="1">
         <v>-2011.0933876000011</v>
@@ -848,10 +848,10 @@
         <v>56.9</v>
       </c>
       <c r="F9">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1">
-        <v>17433.099200000001</v>
+        <v>16775.2464</v>
       </c>
       <c r="H9" s="1">
         <v>-1282.8129599999995</v>
@@ -906,10 +906,10 @@
         <v>16.594000000000001</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>14442.859200000001</v>
+        <v>13239.2876</v>
       </c>
       <c r="H11" s="1">
         <v>-5529.2079304000017</v>
@@ -964,10 +964,10 @@
         <v>95.08</v>
       </c>
       <c r="F13">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G13" s="1">
-        <v>7737.2460000000001</v>
+        <v>7512.9780000000001</v>
       </c>
       <c r="H13" s="1">
         <v>-2924.4547199999997</v>
@@ -993,10 +993,10 @@
         <v>77.56</v>
       </c>
       <c r="F14">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" s="1">
-        <v>9658.4752000000008</v>
+        <v>9531.39</v>
       </c>
       <c r="H14" s="1">
         <v>-198.25291200000029</v>
